--- a/output/pdf_financials_xlsx/DYA.xlsx
+++ b/output/pdf_financials_xlsx/DYA.xlsx
@@ -1807,19 +1807,19 @@
         <v>-1.626522</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1.710825</v>
+        <v>-1.710825</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.876345</v>
+        <v>-4.876345</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>6.623234</v>
+        <v>-6.623234</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>-16.324637</v>
@@ -2099,19 +2099,19 @@
         <v>-1.626522</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.710825</v>
+        <v>-1.710825</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.876345</v>
+        <v>-4.876345</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>6.623234</v>
+        <v>-6.623234</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>-16.324637</v>
@@ -2276,19 +2276,19 @@
         <v>-1.626522</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.710825</v>
+        <v>-1.710825</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.876345</v>
+        <v>-4.876345</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.623234</v>
+        <v>-6.623234</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-16.324637</v>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>243.81725</v>
+        <v>-243.81725</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>236.544071</v>
+        <v>-236.544071</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>253.631133</v>
+        <v>-253.631133</v>
       </c>
       <c r="L32" s="1" t="inlineStr">
         <is>
@@ -2558,19 +2558,19 @@
         <v>-1.626522</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.710825</v>
+        <v>-1.710825</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.876345</v>
+        <v>-4.876345</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>6.623234</v>
+        <v>-6.623234</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>-16.324637</v>
@@ -2676,19 +2676,19 @@
         <v>-1.548813</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.793691</v>
+        <v>-1.627959</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4.877769</v>
+        <v>-4.874921</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>6.664383</v>
+        <v>-6.582085</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>11.508128</v>
+        <v>-11.318674</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>12.752667</v>
+        <v>-12.579579</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>-16.162909</v>
@@ -2747,13 +2747,13 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>2708.21805916775</v>
+        <v>-2674.774463589077</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>12560.71600087317</v>
+        <v>-12353.93363894346</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1197.853050880731</v>
+        <v>-1181.594962367101</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>-2135.121043273334</v>
@@ -2800,19 +2800,19 @@
         <v>-0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>-0</v>
@@ -2871,13 +2871,13 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2691.496261378413</v>
+        <v>-2691.496261378413</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>12457.32481990832</v>
+        <v>-12457.32481990832</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>1189.724006623916</v>
+        <v>-1189.724006623916</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>-2156.485319721744</v>
@@ -6930,46 +6930,46 @@
         <v>1.853369</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>5.132076</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>5.412596</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>5.982222</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>6.103527</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>2.185814</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>3.850324</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>5.137538</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>7.673027</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>11.893511</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>13.934815</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>12.118821</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>9.768758999999999</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>8.717483</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>6.853073</v>
       </c>
     </row>
     <row r="108">
@@ -7307,7 +7307,7 @@
         <v>-11.413401</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>-16.324637</v>
@@ -7528,10 +7528,10 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.007984</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.00394</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
@@ -11871,7 +11871,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11965,7 +11969,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -12547,7 +12555,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12641,7 +12653,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13407,7 +13423,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13499,7 +13519,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -15331,7 +15355,11 @@
           <t>Warrant reserve (note 14)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -15425,7 +15453,11 @@
           <t>Share-based payments reserve (note 13)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16961,7 +16993,11 @@
           <t>Warrant reserve (note 9)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -17055,7 +17091,11 @@
           <t>Share-based payments reserve (note 9)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18029,7 +18069,11 @@
           <t>Warrant reserve (note 8)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18125,7 +18169,11 @@
           <t>Share-based payments reserve (note 8)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -19663,7 +19711,11 @@
           <t>Warrant reserve (note 10)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -19755,7 +19807,11 @@
           <t>Share based payment reserve (note 10)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20805,7 +20861,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -21761,7 +21821,11 @@
           <t>Warrant Reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -21853,7 +21917,11 @@
           <t>Share based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -23197,7 +23265,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E144" s="5" t="n">
         <v>0.112644</v>
       </c>
@@ -40331,7 +40403,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -48108,10 +48184,10 @@
         </is>
       </c>
       <c r="N407" s="5" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="O407" s="5" t="n">
-        <v>12.666123</v>
+        <v>-12.666123</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -48855,16 +48931,16 @@
         </is>
       </c>
       <c r="K415" s="5" t="n">
-        <v>1.710825</v>
+        <v>-1.710825</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>4.876345</v>
+        <v>-4.876345</v>
       </c>
       <c r="M415" s="5" t="n">
-        <v>6.623234</v>
+        <v>-6.623234</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>11.413401</v>
+        <v>-11.413401</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DYA.xlsx
+++ b/output/pdf_financials_xlsx/DYA.xlsx
@@ -715,11 +715,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>0.089726</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.188342</v>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3431,10 +3435,10 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>0.57424</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>0.099966</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0.024351</v>
@@ -3443,10 +3447,10 @@
         <v>0.006624</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>0.036918</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>0.001954</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.925919</v>
@@ -3455,7 +3459,7 @@
         <v>2.875638</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>0.009174</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>0.109327</v>
@@ -3541,10 +3545,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>0.57424</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.099966</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.024351</v>
@@ -3553,10 +3557,10 @@
         <v>0.006624</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>0.036918</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>0.001954</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.925919</v>
@@ -3565,7 +3569,7 @@
         <v>2.875638</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>0.009174</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.109327</v>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>4.964064</v>
+        <v>4.389824</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>6.866212</v>
+        <v>6.766246</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0</v>
@@ -4213,10 +4217,10 @@
         <v>0.007985000000000001</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.040963</v>
+        <v>0.004045</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.011082</v>
+        <v>0.009128000000000001</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0</v>
@@ -4225,7 +4229,7 @@
         <v>0.124464</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.199922</v>
+        <v>0.190748</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>0.529821</v>
@@ -15745,7 +15749,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -18559,7 +18563,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -20669,7 +20673,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -22977,7 +22981,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -43807,7 +43811,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">

--- a/output/pdf_financials_xlsx/DYA.xlsx
+++ b/output/pdf_financials_xlsx/DYA.xlsx
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>0.006494</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>0.020851</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>0.042693</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>0.036325</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>0.040773</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>0.071336</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>1.719965</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.295833</v>
+        <v>1.367169</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>6.869314</v>
@@ -1519,7 +1519,7 @@
         <v>-1.719965</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-1.295833</v>
+        <v>-1.367169</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-6.725814</v>
@@ -2630,25 +2630,25 @@
         <v>0.041149</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.09472700000000001</v>
+        <v>0.21147</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.086544</v>
+        <v>0.251808</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0.161728</v>
+        <v>0.512054</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0.168804</v>
+        <v>0.608195</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.152055</v>
+        <v>0.518857</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.139132</v>
+        <v>0.433396</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0.128011</v>
+        <v>0.357512</v>
       </c>
     </row>
     <row r="35">
@@ -2689,25 +2689,25 @@
         <v>-6.582085</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-11.318674</v>
+        <v>-11.201931</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-12.579579</v>
+        <v>-12.414315</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-16.162909</v>
+        <v>-15.812583</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-10.787541</v>
+        <v>-10.34815</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-8.477446</v>
+        <v>-8.110644000000001</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-10.019691</v>
+        <v>-9.725427</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>-10.293794</v>
+        <v>-10.064293</v>
       </c>
     </row>
     <row r="36">
@@ -2754,25 +2754,25 @@
         <v>-2674.774463589077</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-12353.93363894346</v>
+        <v>-12226.51277013752</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1181.594962367101</v>
+        <v>-1166.071779130155</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-2135.121043273334</v>
+        <v>-2088.84296210578</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-938.8136051958946</v>
+        <v>-900.5744690664812</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1897.271626572491</v>
+        <v>-1815.180507717821</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-625.4637126223968</v>
+        <v>-607.0947375780449</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1598.579046920958</v>
+        <v>-1562.938593085627</v>
       </c>
     </row>
     <row r="37">
@@ -7363,31 +7363,31 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.001424</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.041149</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.21147</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.251808</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.512054</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.608195</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.518857</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.433396</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.357512</v>
       </c>
     </row>
     <row r="116">
@@ -8104,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>0</v>
+        <v>0.063597</v>
       </c>
       <c r="M127" s="3" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -25071,7 +25071,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -33909,7 +33913,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -35343,7 +35351,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -51007,7 +51015,11 @@
           <t>Rent and occupancy costs (note 9)</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -53779,7 +53791,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -60229,7 +60245,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
